--- a/stories/arbres/TREE-TMP-041.xlsx
+++ b/stories/arbres/TREE-TMP-041.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Sami est avec maman, à l'école. Sami a envie de jouer. maman est là, tout près. On va apprendre : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami écoute maman. Sami entend les mots : soleil jour, lune nuit, dodo la nuit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sami va vers le bac à sable. L'eau coule, tout petit bruit. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Sami se souvient : soleil jour, lune nuit, dodo la nuit. Voici le geste : nommer ; se coucher la nuit. On montre du doigt, sans courir. maman dit : je suis là. On reste ensemble.</t>
+          <t>Sami va vers le bac à sable. L'eau coule, tout petit bruit. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Sami se souvient : soleil jour, lune nuit, dodo la nuit. Voici le geste : nommer ; se coucher la nuit. On montre du doigt, sans courir. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Sami va vers le bac à sable. L'eau coule, tout petit bruit. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Sami se souvient : soleil jour, lune nuit, dodo la nuit. Voici le geste : nommer ; se coucher la nuit. On montre du doigt, sans courir.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1862,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Soleil, lune, étoiles.</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2035,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : nommer ; se coucher la nuit. Sami respire. Sami retient : soleil jour, lune nuit, dodo la nuit. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2187,6 +2230,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2349,6 +2397,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le ballon. La lumière est claire. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : nommer ; se coucher la nuit. Sami répète tout bas : soleil jour, lune nuit, dodo la nuit. On se tient la main. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2537,6 +2590,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2701,6 +2759,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Tom. Les chaussures font toc toc. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le ballon et Tom. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2863,6 +2926,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3025,6 +3093,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Léa. La couverture est douce. On rit un peu. Cette fin-là est celle de le bac à sable, le ballon et Léa. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3187,6 +3260,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3349,6 +3427,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Sami. On entend un oiseau. On se tait une seconde. Cette fin-là est celle de le bac à sable, le ballon et Sami. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3511,6 +3594,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3673,6 +3761,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le seau. Il y a des miettes sur la table. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : nommer ; se coucher la nuit. Sami répète tout bas : soleil jour, lune nuit, dodo la nuit. On range un objet. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3861,6 +3954,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4025,6 +4123,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Tom. La couverture est douce. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le seau et Tom. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4187,6 +4290,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4349,6 +4457,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Léa. On entend un oiseau. On rit un peu. Cette fin-là est celle de le bac à sable, le seau et Léa. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4511,6 +4624,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4673,6 +4791,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Sami. Ça sent le pain chaud. On se tait une seconde. Cette fin-là est celle de le bac à sable, le seau et Sami. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4835,6 +4958,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4997,6 +5125,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le doudou. Un chat miaule une fois. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : nommer ; se coucher la nuit. Sami répète tout bas : soleil jour, lune nuit, dodo la nuit. On dit merci. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5185,6 +5318,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5349,6 +5487,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Tom. On entend un oiseau. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le doudou et Tom. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5511,6 +5654,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5673,6 +5821,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Léa. Ça sent le pain chaud. On rit un peu. Cette fin-là est celle de le bac à sable, le doudou et Léa. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5835,6 +5988,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5997,6 +6155,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Sami. Le vent est doux. On se tait une seconde. Cette fin-là est celle de le bac à sable, le doudou et Sami. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6159,6 +6322,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6183,7 +6351,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Sami va vers le toboggan. Un vélo passe au loin. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Sami se souvient : soleil jour, lune nuit, dodo la nuit. Voici le geste : nommer ; se coucher la nuit. On rit un peu. maman dit : je suis là. On reste ensemble.</t>
+          <t>Sami va vers le toboggan. Un vélo passe au loin. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Sami se souvient : soleil jour, lune nuit, dodo la nuit. Voici le geste : nommer ; se coucher la nuit. On rit un peu. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6321,6 +6489,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Sami va vers le toboggan. Un vélo passe au loin. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Sami se souvient : soleil jour, lune nuit, dodo la nuit. Voici le geste : nommer ; se coucher la nuit. On rit un peu.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6501,6 +6675,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Soleil, lune, étoiles.</t>
         </is>
       </c>
     </row>
@@ -6669,6 +6848,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : nommer ; se coucher la nuit. Sami respire. Sami retient : soleil jour, lune nuit, dodo la nuit. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6859,6 +7043,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7021,6 +7210,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le ballon. Les chaussures font toc toc. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : nommer ; se coucher la nuit. Sami répète tout bas : soleil jour, lune nuit, dodo la nuit. On se tient la main. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7209,6 +7403,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7373,6 +7572,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Tom. La couverture est douce. On rit un peu. Cette fin-là est celle de le toboggan, le ballon et Tom. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7535,6 +7739,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7697,6 +7906,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Léa. On entend un oiseau. On se tait une seconde. Cette fin-là est celle de le toboggan, le ballon et Léa. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7859,6 +8073,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8021,6 +8240,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Sami. Ça sent le pain chaud. On se tient la main. Cette fin-là est celle de le toboggan, le ballon et Sami. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8183,6 +8407,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8345,6 +8574,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le seau. La couverture est douce. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : nommer ; se coucher la nuit. Sami répète tout bas : soleil jour, lune nuit, dodo la nuit. On range un objet. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8533,6 +8767,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8697,6 +8936,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Tom. On entend un oiseau. On rit un peu. Cette fin-là est celle de le toboggan, le seau et Tom. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8859,6 +9103,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9021,6 +9270,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Léa. Ça sent le pain chaud. On se tait une seconde. Cette fin-là est celle de le toboggan, le seau et Léa. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9183,6 +9437,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9345,6 +9604,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Sami. Le vent est doux. On se tient la main. Cette fin-là est celle de le toboggan, le seau et Sami. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9507,6 +9771,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9669,6 +9938,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le doudou. On entend un oiseau. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : nommer ; se coucher la nuit. Sami répète tout bas : soleil jour, lune nuit, dodo la nuit. On dit merci. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9857,6 +10131,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10021,6 +10300,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Tom. Ça sent le pain chaud. On rit un peu. Cette fin-là est celle de le toboggan, le doudou et Tom. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10183,6 +10467,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10345,6 +10634,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Léa. Le vent est doux. On se tait une seconde. Cette fin-là est celle de le toboggan, le doudou et Léa. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10507,6 +10801,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10669,6 +10968,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Sami. Le sol est un peu froid. On se tient la main. Cette fin-là est celle de le toboggan, le doudou et Sami. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10831,6 +11135,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10855,7 +11164,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Sami va vers les balançoires. La lumière est claire. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Sami se souvient : soleil jour, lune nuit, dodo la nuit. Voici le geste : nommer ; se coucher la nuit. On se tait une seconde. maman dit : je suis là. On reste ensemble.</t>
+          <t>Sami va vers les balançoires. La lumière est claire. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Sami se souvient : soleil jour, lune nuit, dodo la nuit. Voici le geste : nommer ; se coucher la nuit. On se tait une seconde. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10993,6 +11302,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Sami va vers les balançoires. La lumière est claire. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Sami se souvient : soleil jour, lune nuit, dodo la nuit. Voici le geste : nommer ; se coucher la nuit. On se tait une seconde.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11173,6 +11488,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Soleil, lune, étoiles.</t>
         </is>
       </c>
     </row>
@@ -11341,6 +11661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : nommer ; se coucher la nuit. Sami respire. Sami retient : soleil jour, lune nuit, dodo la nuit. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11531,6 +11856,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11693,6 +12023,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le ballon. Ça sent le pain chaud. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : nommer ; se coucher la nuit. Sami répète tout bas : soleil jour, lune nuit, dodo la nuit. On se tient la main. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11881,6 +12216,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12045,6 +12385,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Tom. On entend un oiseau. On se tait une seconde. Cette fin-là est celle de les balançoires, le ballon et Tom. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12207,6 +12552,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12369,6 +12719,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Léa. Ça sent le pain chaud. On se tient la main. Cette fin-là est celle de les balançoires, le ballon et Léa. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12531,6 +12886,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12693,6 +13053,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Sami. Le vent est doux. On range un objet. Cette fin-là est celle de les balançoires, le ballon et Sami. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12855,6 +13220,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13017,6 +13387,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le seau. Le vent est doux. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : nommer ; se coucher la nuit. Sami répète tout bas : soleil jour, lune nuit, dodo la nuit. On range un objet. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13205,6 +13580,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13369,6 +13749,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Tom. Ça sent le pain chaud. On se tait une seconde. Cette fin-là est celle de les balançoires, le seau et Tom. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13531,6 +13916,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13693,6 +14083,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Léa. Le vent est doux. On se tient la main. Cette fin-là est celle de les balançoires, le seau et Léa. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13855,6 +14250,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14017,6 +14417,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Sami. Le sol est un peu froid. On range un objet. Cette fin-là est celle de les balançoires, le seau et Sami. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14179,6 +14584,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14341,6 +14751,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le doudou. Le sol est un peu froid. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : nommer ; se coucher la nuit. Sami répète tout bas : soleil jour, lune nuit, dodo la nuit. On dit merci. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14529,6 +14944,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14693,6 +15113,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Tom. Le vent est doux. On se tait une seconde. Cette fin-là est celle de les balançoires, le doudou et Tom. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14855,6 +15280,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15017,6 +15447,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Léa. Le sol est un peu froid. On se tient la main. Cette fin-là est celle de les balançoires, le doudou et Léa. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15179,6 +15614,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15341,6 +15781,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint Sami. Une feuille tombe. On range un objet. Cette fin-là est celle de les balançoires, le doudou et Sami. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15503,6 +15948,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15521,7 +15971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15594,6 +16044,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-TMP-041.xlsx
+++ b/stories/arbres/TREE-TMP-041.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Sami est avec maman, à l'école. Sami a envie de jouer. maman est là, tout près. On va apprendre : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami écoute maman. Sami entend les mots : soleil jour, lune nuit, dodo la nuit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1869,6 +1877,7 @@
           <t>narrateur|Que fait-on ? Soleil, lune, étoiles.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2040,6 +2049,7 @@
           <t>narrateur|Oui. Voici le geste : nommer ; se coucher la nuit. Sami respire. Sami retient : soleil jour, lune nuit, dodo la nuit. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2235,6 +2245,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2402,6 +2413,7 @@
           <t>narrateur|Sami a choisi le ballon. La lumière est claire. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : nommer ; se coucher la nuit. Sami répète tout bas : soleil jour, lune nuit, dodo la nuit. On se tient la main. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2597,6 +2609,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2764,6 +2777,7 @@
           <t>narrateur|Sami rejoint Tom. Les chaussures font toc toc. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le ballon et Tom. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2931,6 +2945,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3098,6 +3113,7 @@
           <t>narrateur|Sami rejoint Léa. La couverture est douce. On rit un peu. Cette fin-là est celle de le bac à sable, le ballon et Léa. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3265,6 +3281,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3432,6 +3449,7 @@
           <t>narrateur|Sami rejoint Sami. On entend un oiseau. On se tait une seconde. Cette fin-là est celle de le bac à sable, le ballon et Sami. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3599,6 +3617,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3766,6 +3785,7 @@
           <t>narrateur|Sami a choisi le seau. Il y a des miettes sur la table. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : nommer ; se coucher la nuit. Sami répète tout bas : soleil jour, lune nuit, dodo la nuit. On range un objet. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3961,6 +3981,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4128,6 +4149,7 @@
           <t>narrateur|Sami rejoint Tom. La couverture est douce. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le seau et Tom. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4295,6 +4317,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4462,6 +4485,7 @@
           <t>narrateur|Sami rejoint Léa. On entend un oiseau. On rit un peu. Cette fin-là est celle de le bac à sable, le seau et Léa. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4629,6 +4653,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4796,6 +4821,7 @@
           <t>narrateur|Sami rejoint Sami. Ça sent le pain chaud. On se tait une seconde. Cette fin-là est celle de le bac à sable, le seau et Sami. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4963,6 +4989,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5130,6 +5157,7 @@
           <t>narrateur|Sami a choisi le doudou. Un chat miaule une fois. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : nommer ; se coucher la nuit. Sami répète tout bas : soleil jour, lune nuit, dodo la nuit. On dit merci. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5325,6 +5353,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5492,6 +5521,7 @@
           <t>narrateur|Sami rejoint Tom. On entend un oiseau. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le doudou et Tom. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5659,6 +5689,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5826,6 +5857,7 @@
           <t>narrateur|Sami rejoint Léa. Ça sent le pain chaud. On rit un peu. Cette fin-là est celle de le bac à sable, le doudou et Léa. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5993,6 +6025,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6160,6 +6193,7 @@
           <t>narrateur|Sami rejoint Sami. Le vent est doux. On se tait une seconde. Cette fin-là est celle de le bac à sable, le doudou et Sami. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6327,6 +6361,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6495,6 +6530,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6682,6 +6718,7 @@
           <t>narrateur|Que fait-on ? Soleil, lune, étoiles.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6853,6 +6890,7 @@
           <t>narrateur|Oui. Voici le geste : nommer ; se coucher la nuit. Sami respire. Sami retient : soleil jour, lune nuit, dodo la nuit. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7048,6 +7086,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7215,6 +7254,7 @@
           <t>narrateur|Sami a choisi le ballon. Les chaussures font toc toc. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : nommer ; se coucher la nuit. Sami répète tout bas : soleil jour, lune nuit, dodo la nuit. On se tient la main. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7410,6 +7450,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7577,6 +7618,7 @@
           <t>narrateur|Sami rejoint Tom. La couverture est douce. On rit un peu. Cette fin-là est celle de le toboggan, le ballon et Tom. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7744,6 +7786,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7911,6 +7954,7 @@
           <t>narrateur|Sami rejoint Léa. On entend un oiseau. On se tait une seconde. Cette fin-là est celle de le toboggan, le ballon et Léa. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8078,6 +8122,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8245,6 +8290,7 @@
           <t>narrateur|Sami rejoint Sami. Ça sent le pain chaud. On se tient la main. Cette fin-là est celle de le toboggan, le ballon et Sami. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8412,6 +8458,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8579,6 +8626,7 @@
           <t>narrateur|Sami a choisi le seau. La couverture est douce. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : nommer ; se coucher la nuit. Sami répète tout bas : soleil jour, lune nuit, dodo la nuit. On range un objet. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8774,6 +8822,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8941,6 +8990,7 @@
           <t>narrateur|Sami rejoint Tom. On entend un oiseau. On rit un peu. Cette fin-là est celle de le toboggan, le seau et Tom. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9108,6 +9158,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9275,6 +9326,7 @@
           <t>narrateur|Sami rejoint Léa. Ça sent le pain chaud. On se tait une seconde. Cette fin-là est celle de le toboggan, le seau et Léa. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9442,6 +9494,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9609,6 +9662,7 @@
           <t>narrateur|Sami rejoint Sami. Le vent est doux. On se tient la main. Cette fin-là est celle de le toboggan, le seau et Sami. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9776,6 +9830,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9943,6 +9998,7 @@
           <t>narrateur|Sami a choisi le doudou. On entend un oiseau. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : nommer ; se coucher la nuit. Sami répète tout bas : soleil jour, lune nuit, dodo la nuit. On dit merci. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10138,6 +10194,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10305,6 +10362,7 @@
           <t>narrateur|Sami rejoint Tom. Ça sent le pain chaud. On rit un peu. Cette fin-là est celle de le toboggan, le doudou et Tom. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10472,6 +10530,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10639,6 +10698,7 @@
           <t>narrateur|Sami rejoint Léa. Le vent est doux. On se tait une seconde. Cette fin-là est celle de le toboggan, le doudou et Léa. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10806,6 +10866,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10973,6 +11034,7 @@
           <t>narrateur|Sami rejoint Sami. Le sol est un peu froid. On se tient la main. Cette fin-là est celle de le toboggan, le doudou et Sami. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11140,6 +11202,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11308,6 +11371,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11495,6 +11559,7 @@
           <t>narrateur|Que fait-on ? Soleil, lune, étoiles.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11666,6 +11731,7 @@
           <t>narrateur|Oui. Voici le geste : nommer ; se coucher la nuit. Sami respire. Sami retient : soleil jour, lune nuit, dodo la nuit. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11861,6 +11927,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12028,6 +12095,7 @@
           <t>narrateur|Sami a choisi le ballon. Ça sent le pain chaud. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : nommer ; se coucher la nuit. Sami répète tout bas : soleil jour, lune nuit, dodo la nuit. On se tient la main. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12223,6 +12291,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12390,6 +12459,7 @@
           <t>narrateur|Sami rejoint Tom. On entend un oiseau. On se tait une seconde. Cette fin-là est celle de les balançoires, le ballon et Tom. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12557,6 +12627,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12724,6 +12795,7 @@
           <t>narrateur|Sami rejoint Léa. Ça sent le pain chaud. On se tient la main. Cette fin-là est celle de les balançoires, le ballon et Léa. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12891,6 +12963,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13058,6 +13131,7 @@
           <t>narrateur|Sami rejoint Sami. Le vent est doux. On range un objet. Cette fin-là est celle de les balançoires, le ballon et Sami. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13225,6 +13299,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13392,6 +13467,7 @@
           <t>narrateur|Sami a choisi le seau. Le vent est doux. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : nommer ; se coucher la nuit. Sami répète tout bas : soleil jour, lune nuit, dodo la nuit. On range un objet. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13587,6 +13663,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13754,6 +13831,7 @@
           <t>narrateur|Sami rejoint Tom. Ça sent le pain chaud. On se tait une seconde. Cette fin-là est celle de les balançoires, le seau et Tom. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13921,6 +13999,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14088,6 +14167,7 @@
           <t>narrateur|Sami rejoint Léa. Le vent est doux. On se tient la main. Cette fin-là est celle de les balançoires, le seau et Léa. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14255,6 +14335,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14422,6 +14503,7 @@
           <t>narrateur|Sami rejoint Sami. Le sol est un peu froid. On range un objet. Cette fin-là est celle de les balançoires, le seau et Sami. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14589,6 +14671,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14756,6 +14839,7 @@
           <t>narrateur|Sami a choisi le doudou. Le sol est un peu froid. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : nommer ; se coucher la nuit. Sami répète tout bas : soleil jour, lune nuit, dodo la nuit. On dit merci. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14951,6 +15035,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15118,6 +15203,7 @@
           <t>narrateur|Sami rejoint Tom. Le vent est doux. On se tait une seconde. Cette fin-là est celle de les balançoires, le doudou et Tom. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15285,6 +15371,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15452,6 +15539,7 @@
           <t>narrateur|Sami rejoint Léa. Le sol est un peu froid. On se tient la main. Cette fin-là est celle de les balançoires, le doudou et Léa. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15619,6 +15707,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15786,6 +15875,7 @@
           <t>narrateur|Sami rejoint Sami. Une feuille tombe. On range un objet. Cette fin-là est celle de les balançoires, le doudou et Sami. Sami a appris : Soleil, lune, étoiles. Voici le geste : nommer ; se coucher la nuit. Sami a entendu : soleil jour, lune nuit, dodo la nuit. Sami dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15953,6 +16043,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15971,7 +16062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16051,6 +16142,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16065,7 +16170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16252,6 +16357,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
